--- a/stories/arbres/TREE-DIF-020.xlsx
+++ b/stories/arbres/TREE-DIF-020.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Lila est avec papa, dans la chambre. Lila a envie de jouer. papa est là, tout près. On va apprendre : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila écoute papa. Lila entend les mots : répéter, observer d'abord.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers les cubes. Les chaussures font toc toc. papa sourit. Ici, c'est les cubes. Ce n'est pas comme les autres endroits. Lila se souvient : répéter, observer d'abord. Voici le geste : répéter ; attendre. On dit merci. papa dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers les cubes. Les chaussures font toc toc. papa sourit. Ici, c'est les cubes. Ce n'est pas comme les autres endroits. Lila se souvient : répéter, observer d'abord. Voici le geste : répéter ; attendre. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers les cubes. Les chaussures font toc toc. papa sourit. Ici, c'est les cubes. Ce n'est pas comme les autres endroits. Lila se souvient : répéter, observer d'abord. Voici le geste : répéter ; attendre. On dit merci.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus de temps ou de calme.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : répéter ; attendre. Lila respire. Lila retient : répéter, observer d'abord. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi une pomme. On entend un oiseau. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2580,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2747,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat. Le sol est un peu froid. On dit merci. Cette fin-là est celle de les cubes, une pomme et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les cubes, une pomme et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les cubes, une pomme et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi un yaourt. Ça sent le pain chaud. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat. Une feuille tombe. On dit merci. Cette fin-là est celle de les cubes, un yaourt et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les cubes, un yaourt et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4775,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les cubes, un yaourt et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4942,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5109,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi un morceau de pain. Le vent est doux. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5300,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5467,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de les cubes, un morceau de pain et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5634,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5801,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les cubes, un morceau de pain et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les cubes, un morceau de pain et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6163,7 +6331,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le livre. La couverture est douce. papa sourit. Ici, c'est le livre. Ce n'est pas comme les autres endroits. Lila se souvient : répéter, observer d'abord. Voici le geste : répéter ; attendre. On souffle doucement. papa dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers le livre. La couverture est douce. papa sourit. Ici, c'est le livre. Ce n'est pas comme les autres endroits. Lila se souvient : répéter, observer d'abord. Voici le geste : répéter ; attendre. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6301,6 +6469,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers le livre. La couverture est douce. papa sourit. Ici, c'est le livre. Ce n'est pas comme les autres endroits. Lila se souvient : répéter, observer d'abord. Voici le geste : répéter ; attendre. On souffle doucement.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus de temps ou de calme.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : répéter ; attendre. Lila respire. Lila retient : répéter, observer d'abord. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7015,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7182,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi une pomme. Le sol est un peu froid. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le livre, une pomme et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le livre, une pomme et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le livre, une pomme et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi un yaourt. Une feuille tombe. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le livre, un yaourt et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le livre, un yaourt et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule. La lumière est claire. On attend son tour. Cette fin-là est celle de le livre, un yaourt et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9902,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi un morceau de pain. L'eau coule, tout petit bruit. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10093,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10260,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le livre, un morceau de pain et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10427,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10594,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le livre, un morceau de pain et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10761,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10928,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le livre, un morceau de pain et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11095,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11124,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers la dînette. On entend un oiseau. papa sourit. Ici, c'est la dînette. Ce n'est pas comme les autres endroits. Lila se souvient : répéter, observer d'abord. Voici le geste : répéter ; attendre. On écoute jusqu'au bout. papa dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers la dînette. On entend un oiseau. papa sourit. Ici, c'est la dînette. Ce n'est pas comme les autres endroits. Lila se souvient : répéter, observer d'abord. Voici le geste : répéter ; attendre. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11262,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers la dînette. On entend un oiseau. papa sourit. Ici, c'est la dînette. Ce n'est pas comme les autres endroits. Lila se souvient : répéter, observer d'abord. Voici le geste : répéter ; attendre. On écoute jusqu'au bout.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11444,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus de temps ou de calme.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11617,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : répéter ; attendre. Lila respire. Lila retient : répéter, observer d'abord. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11808,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11975,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi une pomme. Un vélo passe au loin. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12166,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12333,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la dînette, une pomme et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12500,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12667,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la dînette, une pomme et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12834,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13001,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la dînette, une pomme et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13168,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13335,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi un yaourt. La lumière est claire. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13526,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13693,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la dînette, un yaourt et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13860,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14027,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien. La lumière est claire. On attend son tour. Cette fin-là est celle de la dînette, un yaourt et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14194,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14361,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la dînette, un yaourt et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14528,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14695,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi un morceau de pain. Il y a des miettes sur la table. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14886,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15053,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la dînette, un morceau de pain et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15220,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15387,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la dînette, un morceau de pain et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15554,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15721,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la dînette, un morceau de pain et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15888,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15928,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-020.xlsx
+++ b/stories/arbres/TREE-DIF-020.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Lila est avec papa, dans la chambre. Lila a envie de jouer. papa est là, tout près. On va apprendre : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila écoute papa. Lila entend les mots : répéter, observer d'abord.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Plus de temps ou de calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : répéter ; attendre. Lila respire. Lila retient : répéter, observer d'abord. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Lila a choisi une pomme. On entend un oiseau. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2583,6 +2595,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2752,6 +2769,7 @@
           <t>narrateur|Lila rejoint le chat. Le sol est un peu froid. On dit merci. Cette fin-là est celle de les cubes, une pomme et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3105,11 @@
           <t>narrateur|Lila rejoint le chien. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les cubes, une pomme et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3445,7 @@
           <t>narrateur|Lila rejoint la poule. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les cubes, une pomme et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3781,7 @@
           <t>narrateur|Lila a choisi un yaourt. Ça sent le pain chaud. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3943,6 +3971,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4112,6 +4145,7 @@
           <t>narrateur|Lila rejoint le chat. Une feuille tombe. On dit merci. Cette fin-là est celle de les cubes, un yaourt et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4481,11 @@
           <t>narrateur|Lila rejoint le chien. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les cubes, un yaourt et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4780,6 +4821,7 @@
           <t>narrateur|Lila rejoint la poule. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les cubes, un yaourt et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4947,6 +4989,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5114,6 +5157,7 @@
           <t>narrateur|Lila a choisi un morceau de pain. Le vent est doux. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5303,6 +5347,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5472,6 +5521,7 @@
           <t>narrateur|Lila rejoint le chat. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de les cubes, un morceau de pain et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5639,6 +5689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5857,11 @@
           <t>narrateur|Lila rejoint le chien. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les cubes, un morceau de pain et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6197,7 @@
           <t>narrateur|Lila rejoint la poule. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les cubes, un morceau de pain et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6365,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6534,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6718,7 @@
           <t>narrateur|Que fait-on ? Plus de temps ou de calme.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6890,7 @@
           <t>narrateur|Oui. Voici le geste : répéter ; attendre. Lila respire. Lila retient : répéter, observer d'abord. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7020,6 +7082,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7187,6 +7250,7 @@
           <t>narrateur|Lila a choisi une pomme. Le sol est un peu froid. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7376,6 +7440,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7545,6 +7614,7 @@
           <t>narrateur|Lila rejoint le chat. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le livre, une pomme et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7782,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7950,11 @@
           <t>narrateur|Lila rejoint le chien. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le livre, une pomme et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8122,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8290,7 @@
           <t>narrateur|Lila rejoint la poule. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le livre, une pomme et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8458,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8626,7 @@
           <t>narrateur|Lila a choisi un yaourt. Une feuille tombe. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8736,6 +8816,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8905,6 +8990,7 @@
           <t>narrateur|Lila rejoint le chat. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le livre, un yaourt et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9158,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9326,11 @@
           <t>narrateur|Lila rejoint le chien. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le livre, un yaourt et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9666,7 @@
           <t>narrateur|Lila rejoint la poule. La lumière est claire. On attend son tour. Cette fin-là est celle de le livre, un yaourt et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9907,6 +10002,7 @@
           <t>narrateur|Lila a choisi un morceau de pain. L'eau coule, tout petit bruit. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10096,6 +10192,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10265,6 +10366,7 @@
           <t>narrateur|Lila rejoint le chat. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le livre, un morceau de pain et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10432,6 +10534,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10599,6 +10702,11 @@
           <t>narrateur|Lila rejoint le chien. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le livre, un morceau de pain et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10766,6 +10874,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10933,6 +11042,7 @@
           <t>narrateur|Lila rejoint la poule. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le livre, un morceau de pain et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11100,6 +11210,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11268,6 +11379,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11451,6 +11563,7 @@
           <t>narrateur|Que fait-on ? Plus de temps ou de calme.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11622,6 +11735,7 @@
           <t>narrateur|Oui. Voici le geste : répéter ; attendre. Lila respire. Lila retient : répéter, observer d'abord. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11813,6 +11927,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11980,6 +12095,7 @@
           <t>narrateur|Lila a choisi une pomme. Un vélo passe au loin. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12169,6 +12285,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12338,6 +12459,7 @@
           <t>narrateur|Lila rejoint le chat. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la dînette, une pomme et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12505,6 +12627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12672,6 +12795,11 @@
           <t>narrateur|Lila rejoint le chien. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la dînette, une pomme et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12839,6 +12967,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13006,6 +13135,7 @@
           <t>narrateur|Lila rejoint la poule. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la dînette, une pomme et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13173,6 +13303,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13340,6 +13471,7 @@
           <t>narrateur|Lila a choisi un yaourt. La lumière est claire. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13529,6 +13661,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13698,6 +13835,7 @@
           <t>narrateur|Lila rejoint le chat. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la dînette, un yaourt et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13865,6 +14003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14032,6 +14171,11 @@
           <t>narrateur|Lila rejoint le chien. La lumière est claire. On attend son tour. Cette fin-là est celle de la dînette, un yaourt et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14199,6 +14343,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14366,6 +14511,7 @@
           <t>narrateur|Lila rejoint la poule. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la dînette, un yaourt et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14533,6 +14679,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,6 +14847,7 @@
           <t>narrateur|Lila a choisi un morceau de pain. Il y a des miettes sur la table. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : répéter ; attendre. Lila répète tout bas : répéter, observer d'abord. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14889,6 +15037,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15058,6 +15211,7 @@
           <t>narrateur|Lila rejoint le chat. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la dînette, un morceau de pain et le chat. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15225,6 +15379,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15392,6 +15547,11 @@
           <t>narrateur|Lila rejoint le chien. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la dînette, un morceau de pain et le chien. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15559,6 +15719,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15726,6 +15887,7 @@
           <t>narrateur|Lila rejoint la poule. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la dînette, un morceau de pain et la poule. Lila a appris : Plus de temps ou de calme. Voici le geste : répéter ; attendre. Lila a entendu : répéter, observer d'abord. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,6 +16055,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15911,7 +16074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15935,6 +16098,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15949,7 +16126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16136,6 +16313,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-020.xlsx
+++ b/stories/arbres/TREE-DIF-020.xlsx
@@ -4446,17 +4446,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'escargot atteint la feuille, le drap tu. Le vent a lâché, et il est venu. Il est arrivé. La lune d'étain a repris sa pâleur. La soupe est prête, dedans. Le bois a failli sécher, trop tôt. La boîte sèche près de la fenêtre, le couvercle entrouvert. Sur la coquille, la lune d'étain reste, pâle. Le drap retombe, sans claquer.</t>
+          <t>L'escargot atteint la feuille, le drap arrêté. Le vent a lâché, et il est venu. Il est arrivé. La lune d'étain a repris sa pâleur. La soupe est prête, dedans. Le bois a failli sécher, trop tôt. La boîte sèche près de la fenêtre, le couvercle entrouvert. Sur la coquille, la lune d'étain reste, pâle. Le drap retombe, sans claquer.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, le drap tu. Le vent a lâché, et il est venu. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; a repris sa pâleur. La soupe est prête, dedans. Le bois a failli sécher, trop tôt. La boîte sèche près de la fenêtre, le couvercle entrouvert. Sur la coquille, la lune d'étain reste, pâle. Le drap retombe, sans claquer.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, le drap arrêté. Le vent a lâché, et il est venu. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; a repris sa pâleur. La soupe est prête, dedans. Le bois a failli sécher, trop tôt. La boîte sèche près de la fenêtre, le couvercle entrouvert. Sur la coquille, la lune d'étain reste, pâle. Le drap retombe, sans claquer.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, le drap tu. Le vent a lâché, et il est venu. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; a repris sa pâleur. La soupe est prête, dedans. Le bois a failli sécher, trop tôt. La boîte sèche près de la fenêtre, le couvercle entrouvert. Sur la coquille, la lune d'étain reste, pâle. Le drap retombe, sans claquer.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, le drap arrêté. Le vent a lâché, et il est venu. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; a repris sa pâleur. La soupe est prête, dedans. Le bois a failli sécher, trop tôt. La boîte sèche près de la fenêtre, le couvercle entrouvert. Sur la coquille, la lune d'étain reste, pâle. Le drap retombe, sans claquer.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'escargot atteint la feuille, le drap tu.
+          <t>narrateur|L'escargot atteint la feuille, le drap arrêté.
 copine|Le vent a lâché, et il est venu.
 enfant-f|Il est arrivé.
 maman|La lune d'étain a repris sa pâleur.
@@ -5007,17 +5007,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus doux. L'escargot sort deux cornes, à l'abri. La boîte attend, le couvercle ouvert. Ici, ça ne claque plus. Le carton s'abrite, derrière le linge. La lune d'étain du début reparaît, pâle. Tu peux marcher. Il avance, Mila.</t>
+          <t>Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus frais. L'escargot sort deux cornes, à l'abri. La boîte attend, le couvercle ouvert. Ici, ça ne claque plus. Le carton s'abrite, derrière le linge. La lune d'étain du début reparaît, pâle. Tu peux marcher. Il avance, Mila.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus doux. L'escargot sort deux cornes, à l'abri. La boîte attend, le couvercle ouvert. Ici, ça ne claque plus. Le carton s'abrite, derrière le linge. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; du début reparaît, pâle. Tu peux marcher. Il avance, Mila.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus frais. L'escargot sort deux cornes, à l'abri. La boîte attend, le couvercle ouvert. Ici, ça ne claque plus. Le carton s'abrite, derrière le linge. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; du début reparaît, pâle. Tu peux marcher. Il avance, Mila.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus doux. L'escargot sort deux cornes, à l'abri. La boîte attend, le couvercle ouvert. Ici, ça ne claque plus. Le carton s'abrite, derrière le linge. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; du début reparaît, pâle. Tu peux marcher. Il avance, Mila. [pause]</t>
+          <t>Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus frais. L'escargot sort deux cornes, à l'abri. La boîte attend, le couvercle ouvert. Ici, ça ne claque plus. Le carton s'abrite, derrière le linge. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; du début reparaît, pâle. Tu peux marcher. Il avance, Mila. [pause]</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -5153,7 +5153,7 @@
         <is>
           <t>enfant-f|Derrière, Nina.
 narrateur|Nina hoche, puis les suit.
-narrateur|Derrière le linge, l'air est plus doux.
+narrateur|Derrière le linge, l'air est plus frais.
 narrateur|L'escargot sort deux cornes, à l'abri.
 narrateur|La boîte attend, le couvercle ouvert.
 maman|Ici, ça ne claque plus.
@@ -7654,17 +7654,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Une perle tombe du compte-gouttes, sur le seuil. Elles gagnent le rebord des bassines. La gouttière chante trop fort, trop vite. Une goutte du verre se perd dans le courant. L'eau emporte tout. L'escargot rentre, la lune d'étain se cache. Il a peur. Nina recule d'un pas, sans un mot. Le filet est trop fort, ici. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Le verre tremble entre tes doigts. On fait comment, alors ? Mila refuse de foncer. Vous trouvez, toutes les deux ?</t>
+          <t>Une goutte tombe du compte-gouttes, sur le seuil. Elles gagnent le rebord des bassines. La gouttière chante trop fort, trop vite. Une goutte du verre se perd dans le courant. L'eau emporte tout. L'escargot rentre, la lune d'étain se cache. Il a peur. Nina recule d'un pas, sans un mot. Le filet est trop fort, ici. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Le verre tremble entre tes doigts. On fait comment, alors ? Mila refuse de foncer. Vous trouvez, toutes les deux ?</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Une perle tombe du compte-gouttes, sur le seuil. Elles gagnent le rebord des bassines. La &lt;emphasis level="moderate"&gt;gouttière&lt;/emphasis&gt; chante trop fort, trop vite. Une goutte du verre se perd dans le courant. L'eau emporte tout. L'escargot rentre, la lune d'étain se cache. Il a peur. Nina recule d'un pas, sans un mot. Le filet est trop fort, ici. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Le verre tremble entre tes doigts. On fait comment, alors ? Mila refuse de foncer. Vous trouvez, toutes les deux ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Une goutte tombe du compte-gouttes, sur le seuil. Elles gagnent le rebord des bassines. La &lt;emphasis level="moderate"&gt;gouttière&lt;/emphasis&gt; chante trop fort, trop vite. Une goutte du verre se perd dans le courant. L'eau emporte tout. L'escargot rentre, la lune d'étain se cache. Il a peur. Nina recule d'un pas, sans un mot. Le filet est trop fort, ici. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Le verre tremble entre tes doigts. On fait comment, alors ? Mila refuse de foncer. Vous trouvez, toutes les deux ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Une perle tombe du compte-gouttes, sur le seuil. Elles gagnent le rebord des bassines. La &lt;emphasis&gt;gouttière&lt;/emphasis&gt; chante trop fort, trop vite. Une goutte du verre se perd dans le courant. L'eau emporte tout. L'escargot rentre, la lune d'étain se cache. Il a peur. Nina recule d'un pas, sans un mot. Le filet est trop fort, ici. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Le verre tremble entre tes doigts. On fait comment, alors ? Mila refuse de foncer. Vous trouvez, toutes les deux ?&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Une goutte tombe du compte-gouttes, sur le seuil. Elles gagnent le rebord des bassines. La &lt;emphasis&gt;gouttière&lt;/emphasis&gt; chante trop fort, trop vite. Une goutte du verre se perd dans le courant. L'eau emporte tout. L'escargot rentre, la lune d'étain se cache. Il a peur. Nina recule d'un pas, sans un mot. Le filet est trop fort, ici. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Le verre tremble entre tes doigts. On fait comment, alors ? Mila refuse de foncer. Vous trouvez, toutes les deux ?&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Une perle tombe du compte-gouttes, sur le seuil.
+          <t>narrateur|Une goutte tombe du compte-gouttes, sur le seuil.
 narrateur|Elles gagnent le rebord des bassines.
 narrateur|La gouttière chante trop fort, trop vite.
 narrateur|Une goutte du verre se perd dans le courant.
@@ -8234,17 +8234,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'escargot atteint la feuille, deux cornes dressées. On a attendu, et il est venu. Il est arrivé. La lune d'étain regarde la feuille. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Une goutte tremble au bout du verre, puis tombe.</t>
+          <t>L'escargot atteint la feuille, deux cornes dressées. On a attendu, et il est venu. Il est arrivé. La lune d'étain regarde la feuille. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Une goutte tremble au bout du verre, puis tombe.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, deux cornes dressées. On a attendu, et il est venu. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; regarde la feuille. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Une goutte tremble au bout du verre, puis tombe.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, deux cornes dressées. On a attendu, et il est venu. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; regarde la feuille. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Une goutte tremble au bout du verre, puis tombe.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, deux cornes dressées. On a attendu, et il est venu. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; regarde la feuille. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Une goutte tremble au bout du verre, puis tombe.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, deux cornes dressées. On a attendu, et il est venu. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; regarde la feuille. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Une goutte tremble au bout du verre, puis tombe.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -8388,7 +8388,7 @@
 papa|La lune d'étain regarde la feuille.
 maman|La soupe est prête, dedans.
 narrateur|Le verre a failli tout verser, trop vite.
-narrateur|Une goutte reste au bout du compte-gouttes, près du savon.
+narrateur|Une goutte reste au bout du compte-gouttes, près de l'évier.
 narrateur|Sur la coquille, la lune d'étain reste, pâle.
 narrateur|Une goutte tremble au bout du verre, puis tombe.</t>
         </is>
@@ -8607,17 +8607,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'escargot gagne la feuille, sans qu'on le pousse. On l'a regardé, et il a choisi. Il savait le bord. La lune d'étain s'est tournée, pile. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Le verre reflète la lune d'étain, un instant.</t>
+          <t>L'escargot gagne la feuille, sans qu'on le pousse. On l'a regardé, et il a choisi. Il savait le bord. La lune d'étain s'est tournée, pile. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Le verre reflète la lune d'étain, un instant.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot gagne la feuille, sans qu'on le pousse. On l'a regardé, et il a choisi. Il savait le bord. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; s'est tournée, pile. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Le verre reflète la lune d'étain, un instant.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot gagne la feuille, sans qu'on le pousse. On l'a regardé, et il a choisi. Il savait le bord. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; s'est tournée, pile. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Le verre reflète la lune d'étain, un instant.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot gagne la feuille, sans qu'on le pousse. On l'a regardé, et il a choisi. Il savait le bord. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; s'est tournée, pile. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Le verre reflète la lune d'étain, un instant.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot gagne la feuille, sans qu'on le pousse. On l'a regardé, et il a choisi. Il savait le bord. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; s'est tournée, pile. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Le verre reflète la lune d'étain, un instant.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -8761,7 +8761,7 @@
 papa|La lune d'étain s'est tournée, pile.
 maman|La soupe est prête, dedans.
 narrateur|Le verre a failli tout verser, trop vite.
-narrateur|Une goutte reste au bout du compte-gouttes, près du savon.
+narrateur|Une goutte reste au bout du compte-gouttes, près de l'évier.
 narrateur|Sur la coquille, la lune d'étain reste, pâle.
 narrateur|Le verre reflète la lune d'étain, un instant.</t>
         </is>
@@ -8980,17 +8980,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'escargot suit le petit filet, jusqu'à la feuille. Celui-là ne l'emportait pas. Il est arrivé. La lune d'étain brille, du bon côté. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Le petit filet chante plus bas, à présent.</t>
+          <t>L'escargot suit le petit filet, jusqu'à la feuille. Celui-là ne l'emportait pas. Il est arrivé. La lune d'étain brille, du bon côté. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Le petit filet chante plus bas, à présent.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot suit le petit filet, jusqu'à la feuille. Celui-là ne l'emportait pas. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; brille, du bon côté. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Le petit filet chante plus bas, à présent.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot suit le petit filet, jusqu'à la feuille. Celui-là ne l'emportait pas. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; brille, du bon côté. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Le petit filet chante plus bas, à présent.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot suit le petit filet, jusqu'à la feuille. Celui-là ne l'emportait pas. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; brille, du bon côté. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Le petit filet chante plus bas, à présent.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot suit le petit filet, jusqu'à la feuille. Celui-là ne l'emportait pas. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; brille, du bon côté. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Le petit filet chante plus bas, à présent.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -9134,7 +9134,7 @@
 papa|La lune d'étain brille, du bon côté.
 maman|La soupe est prête, dedans.
 narrateur|Le verre a failli tout verser, trop vite.
-narrateur|Une goutte reste au bout du compte-gouttes, près du savon.
+narrateur|Une goutte reste au bout du compte-gouttes, près de l'évier.
 narrateur|Sur la coquille, la lune d'étain reste, pâle.
 narrateur|Le petit filet chante plus bas, à présent.</t>
         </is>
@@ -9168,17 +9168,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Une perle tombe du compte-gouttes, sur le seuil. Elles gagnent le passage des draps. Un drap mouillé claque, trop fort. Les gouttes du linge brouillent le chemin d'eau. Je ne vois plus la ligne. Nina recule d'un pas, les mains aux oreilles. C'est trop fort. L'escargot rentre, la lune d'étain se cache. Le vent n'a pas fini. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. L'escargot n'avance plus. On fait comment, Nina ? Mila refuse de foncer. Vous trouvez, toutes les deux ?</t>
+          <t>Une goutte tombe du compte-gouttes, sur le seuil. Elles gagnent le passage des draps. Un drap mouillé claque, trop fort. Les gouttes du linge brouillent le chemin d'eau. Je ne vois plus la ligne. Nina recule d'un pas, les mains aux oreilles. C'est trop fort. L'escargot rentre, la lune d'étain se cache. Le vent n'a pas fini. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. L'escargot n'avance plus. On fait comment, Nina ? Mila refuse de foncer. Vous trouvez, toutes les deux ?</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Une perle tombe du compte-gouttes, sur le seuil. Elles gagnent le passage des draps. Un drap mouillé claque, trop fort. Les gouttes du &lt;emphasis level="moderate"&gt;linge&lt;/emphasis&gt; brouillent le chemin d'eau. Je ne vois plus la ligne. Nina recule d'un pas, les mains aux oreilles. C'est trop fort. L'escargot rentre, la lune d'étain se cache. Le vent n'a pas fini. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. L'escargot n'avance plus. On fait comment, Nina ? Mila refuse de foncer. Vous trouvez, toutes les deux ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Une goutte tombe du compte-gouttes, sur le seuil. Elles gagnent le passage des draps. Un drap mouillé claque, trop fort. Les gouttes du &lt;emphasis level="moderate"&gt;linge&lt;/emphasis&gt; brouillent le chemin d'eau. Je ne vois plus la ligne. Nina recule d'un pas, les mains aux oreilles. C'est trop fort. L'escargot rentre, la lune d'étain se cache. Le vent n'a pas fini. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. L'escargot n'avance plus. On fait comment, Nina ? Mila refuse de foncer. Vous trouvez, toutes les deux ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Une perle tombe du compte-gouttes, sur le seuil. Elles gagnent le passage des draps. Un drap mouillé claque, trop fort. Les gouttes du &lt;emphasis&gt;linge&lt;/emphasis&gt; brouillent le chemin d'eau. Je ne vois plus la ligne. Nina recule d'un pas, les mains aux oreilles. C'est trop fort. L'escargot rentre, la lune d'étain se cache. Le vent n'a pas fini. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. L'escargot n'avance plus. On fait comment, Nina ? Mila refuse de foncer. Vous trouvez, toutes les deux ?&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Une goutte tombe du compte-gouttes, sur le seuil. Elles gagnent le passage des draps. Un drap mouillé claque, trop fort. Les gouttes du &lt;emphasis&gt;linge&lt;/emphasis&gt; brouillent le chemin d'eau. Je ne vois plus la ligne. Nina recule d'un pas, les mains aux oreilles. C'est trop fort. L'escargot rentre, la lune d'étain se cache. Le vent n'a pas fini. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. L'escargot n'avance plus. On fait comment, Nina ? Mila refuse de foncer. Vous trouvez, toutes les deux ?&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Une perle tombe du compte-gouttes, sur le seuil.
+          <t>narrateur|Une goutte tombe du compte-gouttes, sur le seuil.
 narrateur|Elles gagnent le passage des draps.
 narrateur|Un drap mouillé claque, trop fort.
 narrateur|Les gouttes du linge brouillent le chemin d'eau.
@@ -9748,17 +9748,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'escargot atteint la feuille, le drap tu. Le vent a lâché, et il est venu. Il est arrivé. La lune d'étain a repris sa pâleur. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Le vent laisse le drap, et s'en va.</t>
+          <t>L'escargot atteint la feuille, le drap arrêté. Le vent a lâché, et il est venu. Il est arrivé. La lune d'étain a repris sa pâleur. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Le vent laisse le drap, et s'en va.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, le drap tu. Le vent a lâché, et il est venu. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; a repris sa pâleur. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Le vent laisse le drap, et s'en va.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, le drap arrêté. Le vent a lâché, et il est venu. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; a repris sa pâleur. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Le vent laisse le drap, et s'en va.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, le drap tu. Le vent a lâché, et il est venu. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; a repris sa pâleur. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Le vent laisse le drap, et s'en va.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, le drap arrêté. Le vent a lâché, et il est venu. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; a repris sa pâleur. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Le vent laisse le drap, et s'en va.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -9896,13 +9896,13 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'escargot atteint la feuille, le drap tu.
+          <t>narrateur|L'escargot atteint la feuille, le drap arrêté.
 copine|Le vent a lâché, et il est venu.
 enfant-f|Il est arrivé.
 maman|La lune d'étain a repris sa pâleur.
 papa|La soupe est prête, dedans.
 narrateur|Le verre a failli tout verser, trop vite.
-narrateur|Une goutte reste au bout du compte-gouttes, près du savon.
+narrateur|Une goutte reste au bout du compte-gouttes, près de l'évier.
 narrateur|Sur la coquille, la lune d'étain reste, pâle.
 narrateur|Le vent laisse le drap, et s'en va.</t>
         </is>
@@ -10121,17 +10121,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'escargot gagne la feuille, le drap tenu. On l'a tenu, et il a marché. Il est arrivé. La lune d'étain se voit, à présent. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Une goutte du linge rejoint celle du verre.</t>
+          <t>L'escargot gagne la feuille, le drap tenu. On l'a tenu, et il a marché. Il est arrivé. La lune d'étain se voit, à présent. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Une goutte du linge rejoint celle du verre.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot gagne la feuille, le drap tenu. On l'a tenu, et il a marché. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; se voit, à présent. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Une goutte du linge rejoint celle du verre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot gagne la feuille, le drap tenu. On l'a tenu, et il a marché. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; se voit, à présent. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Une goutte du linge rejoint celle du verre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot gagne la feuille, le drap tenu. On l'a tenu, et il a marché. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; se voit, à présent. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Une goutte du linge rejoint celle du verre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot gagne la feuille, le drap tenu. On l'a tenu, et il a marché. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; se voit, à présent. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Une goutte du linge rejoint celle du verre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -10275,7 +10275,7 @@
 maman|La lune d'étain se voit, à présent.
 papa|La soupe est prête, dedans.
 narrateur|Le verre a failli tout verser, trop vite.
-narrateur|Une goutte reste au bout du compte-gouttes, près du savon.
+narrateur|Une goutte reste au bout du compte-gouttes, près de l'évier.
 narrateur|Sur la coquille, la lune d'étain reste, pâle.
 narrateur|Une goutte du linge rejoint celle du verre.</t>
         </is>
@@ -10309,17 +10309,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus doux. L'escargot sort deux cornes, à l'abri. Une goutte tremble au bout du verre. Ici, ça ne claque plus. Le verre reste frais, derrière le linge. La lune d'étain du début reparaît, pâle. Tu peux marcher. Il avance, Mila.</t>
+          <t>Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus frais. L'escargot sort deux cornes, à l'abri. Une goutte tremble au bout du verre. Ici, ça ne claque plus. Le verre reste frais, derrière le linge. La lune d'étain du début reparaît, pâle. Tu peux marcher. Il avance, Mila.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus doux. L'escargot sort deux cornes, à l'abri. Une goutte tremble au bout du verre. Ici, ça ne claque plus. Le verre reste frais, derrière le linge. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; du début reparaît, pâle. Tu peux marcher. Il avance, Mila.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus frais. L'escargot sort deux cornes, à l'abri. Une goutte tremble au bout du verre. Ici, ça ne claque plus. Le verre reste frais, derrière le linge. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; du début reparaît, pâle. Tu peux marcher. Il avance, Mila.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus doux. L'escargot sort deux cornes, à l'abri. Une goutte tremble au bout du verre. Ici, ça ne claque plus. Le verre reste frais, derrière le linge. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; du début reparaît, pâle. Tu peux marcher. Il avance, Mila. [pause]</t>
+          <t>Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus frais. L'escargot sort deux cornes, à l'abri. Une goutte tremble au bout du verre. Ici, ça ne claque plus. Le verre reste frais, derrière le linge. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; du début reparaît, pâle. Tu peux marcher. Il avance, Mila. [pause]</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -10455,7 +10455,7 @@
         <is>
           <t>enfant-f|Derrière, Nina.
 narrateur|Nina hoche, puis les suit.
-narrateur|Derrière le linge, l'air est plus doux.
+narrateur|Derrière le linge, l'air est plus frais.
 narrateur|L'escargot sort deux cornes, à l'abri.
 narrateur|Une goutte tremble au bout du verre.
 maman|Ici, ça ne claque plus.
@@ -10494,17 +10494,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'escargot atteint la feuille, derrière le linge. Là, ça ne claquait plus. Il est arrivé. La lune d'étain a trouvé l'abri. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Derrière le drap, le verre reste frais.</t>
+          <t>L'escargot atteint la feuille, derrière le linge. Là, ça ne claquait plus. Il est arrivé. La lune d'étain a trouvé l'abri. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Derrière le drap, le verre reste frais.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, derrière le linge. Là, ça ne claquait plus. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; a trouvé l'abri. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Derrière le drap, le verre reste frais.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, derrière le linge. Là, ça ne claquait plus. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; a trouvé l'abri. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Derrière le drap, le verre reste frais.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, derrière le linge. Là, ça ne claquait plus. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; a trouvé l'abri. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Derrière le drap, le verre reste frais.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, derrière le linge. Là, ça ne claquait plus. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; a trouvé l'abri. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Derrière le drap, le verre reste frais.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -10648,7 +10648,7 @@
 maman|La lune d'étain a trouvé l'abri.
 papa|La soupe est prête, dedans.
 narrateur|Le verre a failli tout verser, trop vite.
-narrateur|Une goutte reste au bout du compte-gouttes, près du savon.
+narrateur|Une goutte reste au bout du compte-gouttes, près de l'évier.
 narrateur|Sur la coquille, la lune d'étain reste, pâle.
 narrateur|Derrière le drap, le verre reste frais.</t>
         </is>
@@ -10682,17 +10682,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Une perle tombe du compte-gouttes, sur le seuil. Elles gagnent les carreaux du jardin. Les carreaux brillent, trop chauds, trop secs. Les gouttes sèchent avant d'arriver au bout. La trace s'arrête. L'escargot reste collé, sans bouger. Il n'aime pas le chaud. La lune d'étain pâlit, presque éteinte. Le soleil a trop séché. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Le verre chauffe, contre ta paume. On fait comment, alors ? Mila refuse de foncer. Vous trouvez, toutes les deux ?</t>
+          <t>Une goutte tombe du compte-gouttes, sur le seuil. Elles gagnent les carreaux du jardin. Les carreaux brillent, trop chauds, trop secs. Les gouttes sèchent avant d'arriver au bout. La trace s'arrête. L'escargot reste collé, sans bouger. Il n'aime pas le chaud. La lune d'étain pâlit, presque éteinte. Le soleil a trop séché. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Le verre chauffe, contre ta paume. On fait comment, alors ? Mila refuse de foncer. Vous trouvez, toutes les deux ?</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Une perle tombe du compte-gouttes, sur le seuil. Elles gagnent les &lt;emphasis level="moderate"&gt;carreaux&lt;/emphasis&gt; du jardin. Les carreaux brillent, trop chauds, trop secs. Les gouttes sèchent avant d'arriver au bout. La trace s'arrête. L'escargot reste collé, sans bouger. Il n'aime pas le chaud. La lune d'étain pâlit, presque éteinte. Le soleil a trop séché. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Le verre chauffe, contre ta paume. On fait comment, alors ? Mila refuse de foncer. Vous trouvez, toutes les deux ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Une goutte tombe du compte-gouttes, sur le seuil. Elles gagnent les &lt;emphasis level="moderate"&gt;carreaux&lt;/emphasis&gt; du jardin. Les carreaux brillent, trop chauds, trop secs. Les gouttes sèchent avant d'arriver au bout. La trace s'arrête. L'escargot reste collé, sans bouger. Il n'aime pas le chaud. La lune d'étain pâlit, presque éteinte. Le soleil a trop séché. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Le verre chauffe, contre ta paume. On fait comment, alors ? Mila refuse de foncer. Vous trouvez, toutes les deux ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Une perle tombe du compte-gouttes, sur le seuil. Elles gagnent les &lt;emphasis&gt;carreaux&lt;/emphasis&gt; du jardin. Les carreaux brillent, trop chauds, trop secs. Les gouttes sèchent avant d'arriver au bout. La trace s'arrête. L'escargot reste collé, sans bouger. Il n'aime pas le chaud. La lune d'étain pâlit, presque éteinte. Le soleil a trop séché. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Le verre chauffe, contre ta paume. On fait comment, alors ? Mila refuse de foncer. Vous trouvez, toutes les deux ?&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Une goutte tombe du compte-gouttes, sur le seuil. Elles gagnent les &lt;emphasis&gt;carreaux&lt;/emphasis&gt; du jardin. Les carreaux brillent, trop chauds, trop secs. Les gouttes sèchent avant d'arriver au bout. La trace s'arrête. L'escargot reste collé, sans bouger. Il n'aime pas le chaud. La lune d'étain pâlit, presque éteinte. Le soleil a trop séché. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Le verre chauffe, contre ta paume. On fait comment, alors ? Mila refuse de foncer. Vous trouvez, toutes les deux ?&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Une perle tombe du compte-gouttes, sur le seuil.
+          <t>narrateur|Une goutte tombe du compte-gouttes, sur le seuil.
 narrateur|Elles gagnent les carreaux du jardin.
 narrateur|Les carreaux brillent, trop chauds, trop secs.
 narrateur|Les gouttes sèchent avant d'arriver au bout.
@@ -11262,17 +11262,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'escargot atteint la feuille, à l'ombre du pot. L'ombre était plus fraîche. Il est arrivé. La lune d'étain capte l'ombre, puis s'arrête. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. À l'ombre, le verre ne chauffe plus.</t>
+          <t>L'escargot atteint la feuille, à l'ombre du pot. L'ombre était plus fraîche. Il est arrivé. La lune d'étain capte l'ombre, puis s'arrête. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. À l'ombre, le verre ne chauffe plus.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, à l'ombre du pot. L'ombre était plus fraîche. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; capte l'ombre, puis s'arrête. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. À l'ombre, le verre ne chauffe plus.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, à l'ombre du pot. L'ombre était plus fraîche. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; capte l'ombre, puis s'arrête. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. À l'ombre, le verre ne chauffe plus.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, à l'ombre du pot. L'ombre était plus fraîche. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; capte l'ombre, puis s'arrête. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. À l'ombre, le verre ne chauffe plus.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, à l'ombre du pot. L'ombre était plus fraîche. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; capte l'ombre, puis s'arrête. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. À l'ombre, le verre ne chauffe plus.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -11416,7 +11416,7 @@
 papa|La lune d'étain capte l'ombre, puis s'arrête.
 maman|La soupe est prête, dedans.
 narrateur|Le verre a failli tout verser, trop vite.
-narrateur|Une goutte reste au bout du compte-gouttes, près du savon.
+narrateur|Une goutte reste au bout du compte-gouttes, près de l'évier.
 narrateur|Sur la coquille, la lune d'étain reste, pâle.
 narrateur|À l'ombre, le verre ne chauffe plus.</t>
         </is>
@@ -11635,17 +11635,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'escargot suit les gouttes, jusqu'à la feuille. Goutte après goutte, il a marché. Il est arrivé. La lune d'étain brille sur la ligne d'eau. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Goutte après goutte, le bois redevient sombre.</t>
+          <t>L'escargot suit les gouttes, jusqu'à la feuille. Goutte après goutte, il a marché. Il est arrivé. La lune d'étain brille sur la ligne d'eau. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Goutte après goutte, le bois redevient sombre.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot suit les gouttes, jusqu'à la feuille. Goutte après goutte, il a marché. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; brille sur la ligne d'eau. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Goutte après goutte, le bois redevient sombre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot suit les gouttes, jusqu'à la feuille. Goutte après goutte, il a marché. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; brille sur la ligne d'eau. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Goutte après goutte, le bois redevient sombre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot suit les gouttes, jusqu'à la feuille. Goutte après goutte, il a marché. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; brille sur la ligne d'eau. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Goutte après goutte, le bois redevient sombre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot suit les gouttes, jusqu'à la feuille. Goutte après goutte, il a marché. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; brille sur la ligne d'eau. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Goutte après goutte, le bois redevient sombre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -11789,7 +11789,7 @@
 papa|La lune d'étain brille sur la ligne d'eau.
 maman|La soupe est prête, dedans.
 narrateur|Le verre a failli tout verser, trop vite.
-narrateur|Une goutte reste au bout du compte-gouttes, près du savon.
+narrateur|Une goutte reste au bout du compte-gouttes, près de l'évier.
 narrateur|Sur la coquille, la lune d'étain reste, pâle.
 narrateur|Goutte après goutte, le bois redevient sombre.</t>
         </is>
@@ -12008,17 +12008,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'escargot atteint la feuille, sous le pot. La terre était froide, comme il voulait. Il est arrivé. La lune d'étain s'allume, dans le sombre. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Sous le pot, une goutte du verre s'endort.</t>
+          <t>L'escargot atteint la feuille, sous le pot. La terre était froide, comme il voulait. Il est arrivé. La lune d'étain s'allume, dans le sombre. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Sous le pot, une goutte du verre s'endort.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, sous le pot. La terre était froide, comme il voulait. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; s'allume, dans le sombre. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Sous le pot, une goutte du verre s'endort.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, sous le pot. La terre était froide, comme il voulait. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; s'allume, dans le sombre. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Sous le pot, une goutte du verre s'endort.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, sous le pot. La terre était froide, comme il voulait. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; s'allume, dans le sombre. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près du savon. Sur la coquille, la lune d'étain reste, pâle. Sous le pot, une goutte du verre s'endort.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, sous le pot. La terre était froide, comme il voulait. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; s'allume, dans le sombre. La soupe est prête, dedans. Le verre a failli tout verser, trop vite. Une goutte reste au bout du compte-gouttes, près de l'évier. Sur la coquille, la lune d'étain reste, pâle. Sous le pot, une goutte du verre s'endort.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -12162,7 +12162,7 @@
 papa|La lune d'étain s'allume, dans le sombre.
 maman|La soupe est prête, dedans.
 narrateur|Le verre a failli tout verser, trop vite.
-narrateur|Une goutte reste au bout du compte-gouttes, près du savon.
+narrateur|Une goutte reste au bout du compte-gouttes, près de l'évier.
 narrateur|Sur la coquille, la lune d'étain reste, pâle.
 narrateur|Sous le pot, une goutte du verre s'endort.</t>
         </is>
@@ -12196,17 +12196,17 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Mila prend la feuille, froide de pluie. C'est ta maison, tout au bout. Tiens-la comme un toit, pas trop bas. La feuille sent l'herbe et l'eau. Elle la pose trop tôt, trop près. L'escargot rentre, la lune d'étain s'éteint. Il n'en veut pas ! Le sourire de Mila disparaît. Je m'accroupis, à ta hauteur. La boîte et le compte-gouttes, avec vous. Il les pose près des sandales. Les trois affaires partent ensemble. Nina, vite ! Des pas frais sonnent sur le carreau. J'arrive, Mila. Nina reste près du cadre, sans un mot.</t>
+          <t>Mila prend la feuille, froide de pluie. C'est ta maison, au bout du bois. Tiens-la comme un toit, pas trop bas. La feuille sent l'herbe et l'eau. Elle la pose trop tôt, trop près. L'escargot rentre, la lune d'étain s'éteint. Il n'en veut pas ! Le sourire de Mila disparaît. Je m'accroupis, à ta hauteur. La boîte et le compte-gouttes, avec vous. Il les pose près des sandales. Les trois affaires partent ensemble. Nina, vite ! Des pas frais sonnent sur le carreau. J'arrive, Mila. Nina reste près du cadre, sans un mot.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila prend la &lt;emphasis level="moderate"&gt;feuille&lt;/emphasis&gt;, froide de pluie. C'est ta maison, tout au bout. Tiens-la comme un toit, pas trop bas. La feuille sent l'herbe et l'eau. Elle la pose trop tôt, trop près. L'escargot rentre, la lune d'étain s'éteint. Il n'en veut pas ! Le sourire de Mila disparaît. Je m'accroupis, à ta hauteur. La boîte et le compte-gouttes, avec vous. Il les pose près des sandales. Les trois affaires partent ensemble. Nina, vite ! Des pas frais sonnent sur le carreau. J'arrive, Mila. Nina reste près du cadre, sans un mot.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila prend la &lt;emphasis level="moderate"&gt;feuille&lt;/emphasis&gt;, froide de pluie. C'est ta maison, au bout du bois. Tiens-la comme un toit, pas trop bas. La feuille sent l'herbe et l'eau. Elle la pose trop tôt, trop près. L'escargot rentre, la lune d'étain s'éteint. Il n'en veut pas ! Le sourire de Mila disparaît. Je m'accroupis, à ta hauteur. La boîte et le compte-gouttes, avec vous. Il les pose près des sandales. Les trois affaires partent ensemble. Nina, vite ! Des pas frais sonnent sur le carreau. J'arrive, Mila. Nina reste près du cadre, sans un mot.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Mila prend la &lt;emphasis&gt;feuille&lt;/emphasis&gt;, froide de pluie. C'est ta maison, tout au bout. Tiens-la comme un toit, pas trop bas. La feuille sent l'herbe et l'eau. Elle la pose trop tôt, trop près. L'escargot rentre, la lune d'étain s'éteint. Il n'en veut pas ! Le sourire de Mila disparaît. Je m'accroupis, à ta hauteur. La boîte et le compte-gouttes, avec vous. Il les pose près des sandales. Les trois affaires partent ensemble. Nina, vite ! Des pas frais sonnent sur le carreau. J'arrive, Mila. Nina reste près du cadre, sans un mot. [pause]</t>
+          <t>Mila prend la &lt;emphasis&gt;feuille&lt;/emphasis&gt;, froide de pluie. C'est ta maison, au bout du bois. Tiens-la comme un toit, pas trop bas. La feuille sent l'herbe et l'eau. Elle la pose trop tôt, trop près. L'escargot rentre, la lune d'étain s'éteint. Il n'en veut pas ! Le sourire de Mila disparaît. Je m'accroupis, à ta hauteur. La boîte et le compte-gouttes, avec vous. Il les pose près des sandales. Les trois affaires partent ensemble. Nina, vite ! Des pas frais sonnent sur le carreau. J'arrive, Mila. Nina reste près du cadre, sans un mot. [pause]</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -12341,7 +12341,7 @@
       <c r="AW60" t="inlineStr">
         <is>
           <t>narrateur|Mila prend la feuille, froide de pluie.
-enfant-f|C'est ta maison, tout au bout.
+enfant-f|C'est ta maison, au bout du bois.
 maman|Tiens-la comme un toit, pas trop bas.
 narrateur|La feuille sent l'herbe et l'eau.
 narrateur|Elle la pose trop tôt, trop près.
@@ -12575,17 +12575,17 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>On répète, tout bas. La feuille attend, on regarde. Je viens après. Elle a le temps. Nina suit des yeux la nervure verte. Elle ne dit rien, puis hoche. Vous partez quand elle est prête. Oui. La feuille perle, une goutte au bord.</t>
+          <t>On répète, à voix basse. La feuille attend, on regarde. Je viens après. Elle a le temps. Nina suit des yeux la nervure verte. Elle ne dit rien, puis hoche. Vous partez quand elle est prête. Oui. La feuille perle, une goutte au bord.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On répète, tout bas. La feuille attend, on regarde. Je viens après. Elle a le temps. &lt;emphasis level="moderate"&gt;Nina&lt;/emphasis&gt; suit des yeux la nervure verte. Elle ne dit rien, puis hoche. Vous partez quand elle est prête. Oui. La feuille perle, une goutte au bord.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On répète, à voix basse. La feuille attend, on regarde. Je viens après. Elle a le temps. &lt;emphasis level="moderate"&gt;Nina&lt;/emphasis&gt; suit des yeux la nervure verte. Elle ne dit rien, puis hoche. Vous partez quand elle est prête. Oui. La feuille perle, une goutte au bord.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>On répète, tout bas. La feuille attend, on regarde. Je viens après. Elle a le temps. &lt;emphasis&gt;Nina&lt;/emphasis&gt; suit des yeux la nervure verte. Elle ne dit rien, puis hoche. Vous partez quand elle est prête. Oui. La feuille perle, une goutte au bord. [pause]</t>
+          <t>On répète, à voix basse. La feuille attend, on regarde. Je viens après. Elle a le temps. &lt;emphasis&gt;Nina&lt;/emphasis&gt; suit des yeux la nervure verte. Elle ne dit rien, puis hoche. Vous partez quand elle est prête. Oui. La feuille perle, une goutte au bord. [pause]</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>enfant-f|On répète, tout bas.
+          <t>enfant-f|On répète, à voix basse.
 enfant-f|La feuille attend, on regarde.
 copine|Je viens après.
 papa|Elle a le temps.
@@ -15050,17 +15050,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'escargot atteint la feuille, le drap tu. Le vent a lâché, et il est venu. Il est arrivé. La lune d'étain a repris sa pâleur. La soupe est prête, dedans. La feuille a failli s'envoler, trop loin. La feuille sèche sur le rebord, un peu recroquevillée. Sur la coquille, la lune d'étain reste, pâle. Un coin de feuille a séché, l'autre reste froid.</t>
+          <t>L'escargot atteint la feuille, le drap arrêté. Le vent a lâché, et il est venu. Il est arrivé. La lune d'étain a repris sa pâleur. La soupe est prête, dedans. La feuille a failli s'envoler, trop loin. La feuille sèche sur le rebord, un peu recroquevillée. Sur la coquille, la lune d'étain reste, pâle. Un coin de feuille a séché, l'autre reste froid.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, le drap tu. Le vent a lâché, et il est venu. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; a repris sa pâleur. La soupe est prête, dedans. La feuille a failli s'envoler, trop loin. La feuille sèche sur le rebord, un peu recroquevillée. Sur la coquille, la lune d'étain reste, pâle. Un coin de feuille a séché, l'autre reste froid.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'escargot atteint la feuille, le drap arrêté. Le vent a lâché, et il est venu. Il est arrivé. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; a repris sa pâleur. La soupe est prête, dedans. La feuille a failli s'envoler, trop loin. La feuille sèche sur le rebord, un peu recroquevillée. Sur la coquille, la lune d'étain reste, pâle. Un coin de feuille a séché, l'autre reste froid.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, le drap tu. Le vent a lâché, et il est venu. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; a repris sa pâleur. La soupe est prête, dedans. La feuille a failli s'envoler, trop loin. La feuille sèche sur le rebord, un peu recroquevillée. Sur la coquille, la lune d'étain reste, pâle. Un coin de feuille a séché, l'autre reste froid.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'escargot atteint la feuille, le drap arrêté. Le vent a lâché, et il est venu. Il est arrivé. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; a repris sa pâleur. La soupe est prête, dedans. La feuille a failli s'envoler, trop loin. La feuille sèche sur le rebord, un peu recroquevillée. Sur la coquille, la lune d'étain reste, pâle. Un coin de feuille a séché, l'autre reste froid.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'escargot atteint la feuille, le drap tu.
+          <t>narrateur|L'escargot atteint la feuille, le drap arrêté.
 copine|Le vent a lâché, et il est venu.
 enfant-f|Il est arrivé.
 maman|La lune d'étain a repris sa pâleur.
@@ -15611,17 +15611,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus doux. L'escargot sort deux cornes, à l'abri. La feuille perle, une nervure brillante. Ici, ça ne claque plus. La nervure s'abrite, derrière le linge. La lune d'étain du début reparaît, pâle. Tu peux marcher. Il avance, Mila.</t>
+          <t>Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus frais. L'escargot sort deux cornes, à l'abri. La feuille perle, une nervure brillante. Ici, ça ne claque plus. La nervure s'abrite, derrière le linge. La lune d'étain du début reparaît, pâle. Tu peux marcher. Il avance, Mila.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus doux. L'escargot sort deux cornes, à l'abri. La feuille perle, une nervure brillante. Ici, ça ne claque plus. La nervure s'abrite, derrière le linge. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; du début reparaît, pâle. Tu peux marcher. Il avance, Mila.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus frais. L'escargot sort deux cornes, à l'abri. La feuille perle, une nervure brillante. Ici, ça ne claque plus. La nervure s'abrite, derrière le linge. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; du début reparaît, pâle. Tu peux marcher. Il avance, Mila.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus doux. L'escargot sort deux cornes, à l'abri. La feuille perle, une nervure brillante. Ici, ça ne claque plus. La nervure s'abrite, derrière le linge. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; du début reparaît, pâle. Tu peux marcher. Il avance, Mila. [pause]</t>
+          <t>Derrière, Nina. Nina hoche, puis les suit. Derrière le linge, l'air est plus frais. L'escargot sort deux cornes, à l'abri. La feuille perle, une nervure brillante. Ici, ça ne claque plus. La nervure s'abrite, derrière le linge. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; du début reparaît, pâle. Tu peux marcher. Il avance, Mila. [pause]</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -15757,7 +15757,7 @@
         <is>
           <t>enfant-f|Derrière, Nina.
 narrateur|Nina hoche, puis les suit.
-narrateur|Derrière le linge, l'air est plus doux.
+narrateur|Derrière le linge, l'air est plus frais.
 narrateur|L'escargot sort deux cornes, à l'abri.
 narrateur|La feuille perle, une nervure brillante.
 maman|Ici, ça ne claque plus.
@@ -17492,7 +17492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17542,6 +17542,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
